--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/UTAH_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/UTAH_2010.xlsx
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C99">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C162">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C715">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1049">
